--- a/docs/LIVE_SPOtCH_月次PL.xlsx
+++ b/docs/LIVE_SPOtCH_月次PL.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サマリー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year1（2026.7-2027.6）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year2（2027.7-2028.6）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year3（2028.7-2029.6）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year1（2026.6-2027.5）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year2（2027.6-2028.5）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year3（2028.6-2029.5）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提条件" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="返済スケジュール" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
@@ -617,14 +617,14 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LIVE SPOtCH  3年間サマリー</t>
+          <t>LIVE SPOtCH  3年間サマリー（v2）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIN-NAH株式会社 ／ 単位: 円</t>
+          <t>LIN-NAH株式会社 ／ 単位: 円 ／ 2026/6/1正式ローンチ起点</t>
         </is>
       </c>
     </row>
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>291025</v>
+        <v>339025</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1181710</v>
+        <v>1229710</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3386107</v>
+        <v>3434107</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4858842</v>
+        <v>5002842</v>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>5031025</v>
+        <v>5079025</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>6341710</v>
+        <v>6389710</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>14786107</v>
+        <v>14834107</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>26158842</v>
+        <v>26302842</v>
       </c>
     </row>
     <row r="19" ht="8" customHeight="1"/>
@@ -896,16 +896,16 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>-3498025</v>
+        <v>-3546025</v>
       </c>
       <c r="C20" s="14" t="n">
-        <v>6564890</v>
+        <v>6516890</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>36651093</v>
+        <v>36603093</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>39717958</v>
+        <v>39573958</v>
       </c>
     </row>
     <row r="21" ht="8" customHeight="1"/>
@@ -946,16 +946,16 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>-4970353</v>
+        <v>-5018353</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>5092562</v>
+        <v>5044562</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>35178765</v>
+        <v>35130765</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>35300974</v>
+        <v>35156974</v>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
@@ -965,16 +965,16 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>-4970353</v>
+        <v>-5018353</v>
       </c>
       <c r="C25" s="14" t="n">
-        <v>122209</v>
+        <v>26209</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>35300974</v>
+        <v>35156974</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>30452830</v>
+        <v>30164830</v>
       </c>
     </row>
     <row r="26" ht="8" customHeight="1"/>
@@ -1030,7 +1030,7 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>※ 借入条件: 700万円 / 5年返済 / 年利2.0%想定</t>
+          <t>※ 借入条件: 公庫350万 + 埼玉りそな350万 = 700万円 / 5年 / 年利2.0% / 2026/5/末 着金 → 2026/6/1 ローンチ → 2026/6 から返済開始</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1078,14 +1078,14 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LIVE SPOtCH  月次損益計算書（Year 1: 2026年7月〜2027年6月）</t>
+          <t>LIVE SPOtCH  月次損益計算書（Year 1: 2026年6月〜2027年5月）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIN-NAH株式会社 ／ 単位: 円</t>
+          <t>LIN-NAH株式会社 ／ 単位: 円 ／ v2改訂版（2026/05/11）</t>
         </is>
       </c>
     </row>
@@ -1099,62 +1099,62 @@
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>2026/6</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>2026/7</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026/8</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>2026/9</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2026/10</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>2026/11</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>2026/12</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2027/1</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>2027/2</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>2027/3</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>2027/4</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>2027/5</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>2027/6</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1444,358 +1444,358 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>LiveKit Cloud（映像配信）</t>
+          <t>LiveKit Cloud Ship（映像配信）</t>
         </is>
       </c>
       <c r="B13" s="19" t="n"/>
       <c r="C13" s="9" t="n">
-        <v>5240</v>
+        <v>7740</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>5600</v>
+        <v>8100</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>6080</v>
+        <v>8580</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>6680</v>
+        <v>9180</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>8000</v>
+        <v>10500</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>8750</v>
+        <v>11250</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>9350</v>
+        <v>11850</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>10100</v>
+        <v>12600</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>12875</v>
+        <v>15375</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>14750</v>
+        <v>17250</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>17000</v>
+        <v>19500</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>20000</v>
+        <v>22500</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>124425</v>
+        <v>154425</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Supabase（DB・認証）</t>
+          <t>TCP化中継server（B案・配信安定）</t>
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>51000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Vercel（ホスティング）</t>
+          <t>Supabase（DB・認証）</t>
         </is>
       </c>
       <c r="B15" s="19" t="n"/>
       <c r="C15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>37500</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Stripe手数料（3.6%）</t>
+          <t>Vercel（ホスティング）</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>201</v>
+        <v>2500</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>503</v>
+        <v>2500</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>907</v>
+        <v>2500</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1411</v>
+        <v>2500</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>2520</v>
+        <v>2500</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>3146</v>
+        <v>2500</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>3650</v>
+        <v>2500</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>4284</v>
+        <v>2500</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>6613</v>
+        <v>2500</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>8186</v>
+        <v>5000</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>10080</v>
+        <v>5000</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>12599</v>
+        <v>5000</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>54100</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>その他インフラ</t>
+          <t>Stripe手数料（3.6%）</t>
         </is>
       </c>
       <c r="B17" s="19" t="n"/>
       <c r="C17" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>503</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>907</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>1411</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>2520</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>3146</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>3650</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>4284</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>6613</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>8186</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>10080</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>12599</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>54100</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>その他インフラ</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="N17" s="9" t="n">
+      <c r="N18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O18" s="7" t="n">
         <v>24000</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>インフラ費 小計</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="21" t="n">
-        <v>12941</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>13603</v>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>14487</v>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>15591</v>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>18020</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>19396</v>
-      </c>
-      <c r="I18" s="21" t="n">
-        <v>20500</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>21884</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>26988</v>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>37936</v>
-      </c>
-      <c r="M18" s="21" t="n">
-        <v>42080</v>
-      </c>
-      <c r="N18" s="21" t="n">
-        <v>47599</v>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>291025</v>
-      </c>
-    </row>
-    <row r="19" ht="8" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="21" t="n">
+        <v>16941</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>17603</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>18487</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>19591</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>22020</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>23396</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>25884</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>30988</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>41936</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>46080</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>51599</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>339025</v>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>販管費</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>開発費（保守・新機能）</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="9" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>200000</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="O21" s="9" t="n">
-        <v>2100000</v>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>マーケティング費</t>
+          <t>開発費（保守・新機能）</t>
         </is>
       </c>
       <c r="B22" s="18" t="n"/>
@@ -1818,608 +1818,655 @@
         <v>200000</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>2400000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>人件費（CS・運営）</t>
+          <t>マーケティング費</t>
         </is>
       </c>
       <c r="B23" s="19" t="n"/>
       <c r="C23" s="9" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>その他経費</t>
+          <t>人件費（CS・運営）</t>
         </is>
       </c>
       <c r="B24" s="18" t="n"/>
       <c r="C24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>その他経費</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N25" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O25" s="9" t="n">
         <v>240000</v>
       </c>
     </row>
-    <row r="25" ht="8" customHeight="1"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26" ht="8" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>経費 合計（返済前）</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="21" t="n">
-        <v>632941</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>633603</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>634487</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>435591</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>438020</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>439396</v>
-      </c>
-      <c r="I26" s="21" t="n">
-        <v>290500</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <v>291884</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>296988</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <v>307936</v>
-      </c>
-      <c r="M26" s="21" t="n">
-        <v>312080</v>
-      </c>
-      <c r="N26" s="21" t="n">
-        <v>317599</v>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>5031025</v>
-      </c>
-    </row>
-    <row r="27" ht="8" customHeight="1"/>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="21" t="n">
+        <v>636941</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>637603</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>638487</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>439591</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>442020</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>443396</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>294500</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>295884</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>300988</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>311936</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>316080</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>321599</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>5079025</v>
+      </c>
+    </row>
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>営業損益（返済前）</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="13" t="n">
-        <v>-627341</v>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>-619603</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>-609287</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>-396391</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>-368020</v>
-      </c>
-      <c r="H28" s="13" t="n">
-        <v>-351996</v>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>-186200</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>-169484</v>
-      </c>
-      <c r="K28" s="13" t="n">
-        <v>-109088</v>
-      </c>
-      <c r="L28" s="13" t="n">
-        <v>-75336</v>
-      </c>
-      <c r="M28" s="13" t="n">
-        <v>-25680</v>
-      </c>
-      <c r="N28" s="14" t="n">
-        <v>40401</v>
-      </c>
-      <c r="O28" s="23" t="n">
-        <v>-3498025</v>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="13" t="n">
+        <v>-631341</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>-623603</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>-613287</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>-400391</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>-372020</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>-355996</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>-190200</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>-173484</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>-113088</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>-79336</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>-29680</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>36401</v>
+      </c>
+      <c r="O29" s="23" t="n">
+        <v>-3546025</v>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>借入返済</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>月額返済（5年/2.0%/¥122,694）</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="L31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="N31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="O31" s="9" t="n">
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="O32" s="7" t="n">
         <v>1472328</v>
       </c>
     </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>返済後キャッシュフロー</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="13" t="n">
-        <v>-750035</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>-742297</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>-731981</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>-519085</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>-490714</v>
-      </c>
-      <c r="H33" s="13" t="n">
-        <v>-474690</v>
-      </c>
-      <c r="I33" s="13" t="n">
-        <v>-308894</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>-292178</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>-231782</v>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>-198030</v>
-      </c>
-      <c r="M33" s="13" t="n">
-        <v>-148374</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>-82293</v>
-      </c>
-      <c r="O33" s="23" t="n">
-        <v>-4970353</v>
-      </c>
-    </row>
+    <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>累計CF（返済後）</t>
+          <t>返済後キャッシュフロー</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
       <c r="C34" s="13" t="n">
-        <v>-750035</v>
+        <v>-754035</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>-1492332</v>
+        <v>-746297</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>-2224313</v>
+        <v>-735981</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>-2743398</v>
+        <v>-523085</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>-3234112</v>
+        <v>-494714</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>-3708802</v>
+        <v>-478690</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>-4017696</v>
+        <v>-312894</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>-4309874</v>
+        <v>-296178</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>-4541656</v>
+        <v>-235782</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>-4739686</v>
+        <v>-202030</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>-4888060</v>
+        <v>-152374</v>
       </c>
       <c r="N34" s="13" t="n">
-        <v>-4970353</v>
-      </c>
-      <c r="O34" s="13" t="n">
-        <v>-4970353</v>
-      </c>
-    </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+        <v>-86293</v>
+      </c>
+      <c r="O34" s="23" t="n">
+        <v>-5018353</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>累計CF（返済後）</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="13" t="n">
+        <v>-754035</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>-1500332</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>-2236313</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>-2759398</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>-3254112</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>-3732802</v>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>-4045696</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>-4341874</v>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>-4577656</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>-4779686</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>-4932060</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>-5018353</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>-5018353</v>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>登録ユーザー（累計）</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>900</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>3400</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>5200</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>6400</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="O37" s="16" t="n">
-        <v>8000</v>
-      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>有料会員（累計）</t>
+          <t>登録ユーザー（累計）</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>72</v>
+        <v>900</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>112</v>
+        <v>1400</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>290</v>
+        <v>2900</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>340</v>
+        <v>3400</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>525</v>
+        <v>4200</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>650</v>
+        <v>5200</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>800</v>
+        <v>6400</v>
       </c>
       <c r="N38" s="7" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  うち配信者プラン</t>
+          <t>有料会員（累計）</t>
         </is>
       </c>
       <c r="B39" s="19" t="n"/>
       <c r="C39" s="9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>218</v>
+        <v>290</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>394</v>
+        <v>525</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>488</v>
+        <v>650</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="O39" s="16" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  うちチームプラン</t>
+          <t xml:space="preserve">  うち配信者プラン</t>
         </is>
       </c>
       <c r="B40" s="18" t="n"/>
       <c r="C40" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>188</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>218</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>255</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>394</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>488</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  うちチームプラン</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D41" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E41" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F41" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G41" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H41" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I41" s="9" t="n">
         <v>72</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J41" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K41" s="9" t="n">
         <v>131</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="L41" s="9" t="n">
         <v>162</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M41" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N41" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="O40" s="15" t="n">
+      <c r="O41" s="16" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>※ 本計画は見込み数値です。借入条件: 700万円 / 5年返済 / 年利2.0%想定</t>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>※ 本計画は見込み数値です。借入条件: 公庫350万 + 埼玉りそな350万 = 700万円協調融資 / 5年返済 / 年利2.0%想定 / 2026年5月末着金 → 6月1日正式ローンチ → 6月から返済開始</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A43:O43"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A36:O36"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A21:O21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -2433,7 +2480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2456,14 +2503,14 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LIVE SPOtCH  月次損益計算書（Year 2: 2027年7月〜2028年6月）</t>
+          <t>LIVE SPOtCH  月次損益計算書（Year 2: 2027年6月〜2028年5月）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIN-NAH株式会社 ／ 単位: 円</t>
+          <t>LIN-NAH株式会社 ／ 単位: 円 ／ v2改訂版（2026/05/11）</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2524,62 @@
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>2027/6</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>2027/7</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2027/8</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>2027/9</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2027/10</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>2027/11</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>2027/12</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2028/1</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>2028/2</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>2028/3</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>2028/4</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>2028/5</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>2028/6</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -2822,982 +2869,1029 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>LiveKit Cloud（映像配信）</t>
+          <t>LiveKit Cloud Ship（映像配信）</t>
         </is>
       </c>
       <c r="B13" s="19" t="n"/>
       <c r="C13" s="9" t="n">
-        <v>22100</v>
+        <v>24600</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25160</v>
+        <v>27660</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>28580</v>
+        <v>31080</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>32360</v>
+        <v>34860</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>36500</v>
+        <v>39000</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>40100</v>
+        <v>42600</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>46535</v>
+        <v>49035</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>50435</v>
+        <v>52935</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>55310</v>
+        <v>57810</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>60575</v>
+        <v>63075</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>66425</v>
+        <v>68925</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>73250</v>
+        <v>75750</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>537330</v>
+        <v>567330</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Supabase（DB・認証）</t>
+          <t>TCP化中継server（B案・配信安定）</t>
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>138000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Vercel（ホスティング）</t>
+          <t>Supabase（DB・認証）</t>
         </is>
       </c>
       <c r="B15" s="19" t="n"/>
       <c r="C15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>70000</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Stripe手数料（3.6%）</t>
+          <t>Vercel（ホスティング）</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>14774</v>
+        <v>5000</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>17416</v>
+        <v>5000</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>20368</v>
+        <v>5000</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>23637</v>
+        <v>5000</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>27215</v>
+        <v>5000</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>30326</v>
+        <v>5000</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>35881</v>
+        <v>5000</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>39250</v>
+        <v>5000</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>43466</v>
+        <v>5000</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>48013</v>
+        <v>5000</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>53067</v>
+        <v>10000</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>58967</v>
+        <v>10000</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>412380</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>その他インフラ</t>
+          <t>Stripe手数料（3.6%）</t>
         </is>
       </c>
       <c r="B17" s="19" t="n"/>
       <c r="C17" s="9" t="n">
+        <v>14774</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>17416</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>20368</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>23637</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>27215</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>30326</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>35881</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>39250</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>43466</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>48013</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>53067</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>58967</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>412380</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>その他インフラ</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="N17" s="9" t="n">
+      <c r="N18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O18" s="7" t="n">
         <v>24000</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>インフラ費 小計</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="21" t="n">
-        <v>51874</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>57576</v>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>63948</v>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>70997</v>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>78715</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>85426</v>
-      </c>
-      <c r="I18" s="21" t="n">
-        <v>104416</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>111685</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>120776</v>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>130588</v>
-      </c>
-      <c r="M18" s="21" t="n">
-        <v>146492</v>
-      </c>
-      <c r="N18" s="21" t="n">
-        <v>159217</v>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>1181710</v>
-      </c>
-    </row>
-    <row r="19" ht="8" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="21" t="n">
+        <v>55874</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>61576</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>67948</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>74997</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>82715</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>89426</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>108416</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>115685</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>124776</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>134588</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>150492</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>163217</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>1229710</v>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>販管費</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>開発費（保守・新機能）</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="O21" s="9" t="n">
-        <v>960000</v>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>マーケティング費</t>
+          <t>開発費（保守・新機能）</t>
         </is>
       </c>
       <c r="B22" s="18" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>2400000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>人件費（CS・運営）</t>
+          <t>マーケティング費</t>
         </is>
       </c>
       <c r="B23" s="19" t="n"/>
       <c r="C23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>1440000</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>その他経費</t>
+          <t>人件費（CS・運営）</t>
         </is>
       </c>
       <c r="B24" s="18" t="n"/>
       <c r="C24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>1440000</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>その他経費</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N25" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O25" s="9" t="n">
         <v>360000</v>
       </c>
     </row>
-    <row r="25" ht="8" customHeight="1"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26" ht="8" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>経費 合計（返済前）</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="21" t="n">
-        <v>481874</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>487576</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>493948</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>500997</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>508715</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>515426</v>
-      </c>
-      <c r="I26" s="21" t="n">
-        <v>534416</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <v>541685</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>550776</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <v>560588</v>
-      </c>
-      <c r="M26" s="21" t="n">
-        <v>576492</v>
-      </c>
-      <c r="N26" s="21" t="n">
-        <v>589217</v>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>6341710</v>
-      </c>
-    </row>
-    <row r="27" ht="8" customHeight="1"/>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="21" t="n">
+        <v>485874</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>491576</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>497948</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>504997</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>512715</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>519426</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>538416</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>545685</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>554776</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>564588</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>580492</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>593217</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>6389710</v>
+      </c>
+    </row>
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>営業損益（返済前）</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="13" t="n">
-        <v>-61974</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>7424</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>84952</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>170803</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>264785</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>346474</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>533584</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>681915</v>
-      </c>
-      <c r="K28" s="14" t="n">
-        <v>852424</v>
-      </c>
-      <c r="L28" s="14" t="n">
-        <v>1031612</v>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>1219108</v>
-      </c>
-      <c r="N28" s="14" t="n">
-        <v>1433783</v>
-      </c>
-      <c r="O28" s="24" t="n">
-        <v>6564890</v>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="13" t="n">
+        <v>-65974</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>3424</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>80952</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>166803</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>260785</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>342474</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>529584</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>677915</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>848424</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>1027612</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>1215108</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>1429783</v>
+      </c>
+      <c r="O29" s="24" t="n">
+        <v>6516890</v>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>借入返済</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>月額返済（5年/2.0%/¥122,694）</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="L31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="N31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="O31" s="9" t="n">
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="O32" s="7" t="n">
         <v>1472328</v>
       </c>
     </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>返済後キャッシュフロー</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="13" t="n">
-        <v>-184668</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>-115270</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>-37742</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>48109</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>142091</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>223780</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>410890</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>559221</v>
-      </c>
-      <c r="K33" s="14" t="n">
-        <v>729730</v>
-      </c>
-      <c r="L33" s="14" t="n">
-        <v>908918</v>
-      </c>
-      <c r="M33" s="14" t="n">
-        <v>1096414</v>
-      </c>
-      <c r="N33" s="14" t="n">
-        <v>1311089</v>
-      </c>
-      <c r="O33" s="24" t="n">
-        <v>5092562</v>
-      </c>
-    </row>
+    <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>累計CF（返済後）</t>
+          <t>返済後キャッシュフロー</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
       <c r="C34" s="13" t="n">
-        <v>-5155021</v>
+        <v>-188668</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>-5270291</v>
+        <v>-119270</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>-5308033</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>-5259924</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>-5117833</v>
-      </c>
-      <c r="H34" s="13" t="n">
-        <v>-4894053</v>
-      </c>
-      <c r="I34" s="13" t="n">
-        <v>-4483163</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>-3923942</v>
-      </c>
-      <c r="K34" s="13" t="n">
-        <v>-3194212</v>
-      </c>
-      <c r="L34" s="13" t="n">
-        <v>-2285294</v>
-      </c>
-      <c r="M34" s="13" t="n">
-        <v>-1188880</v>
+        <v>-41742</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>44109</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>138091</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>219780</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>406890</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>555221</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>725730</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>904918</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>1092414</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>122209</v>
-      </c>
-      <c r="O34" s="14" t="n">
-        <v>122209</v>
-      </c>
-    </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+        <v>1307089</v>
+      </c>
+      <c r="O34" s="24" t="n">
+        <v>5044562</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>累計CF（返済後）</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="13" t="n">
+        <v>-5207021</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>-5326291</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>-5368033</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>-5323924</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>-5185833</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>-4966053</v>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>-4559163</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>-4003942</v>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>-3278212</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>-2373294</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>-1280880</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>26209</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>26209</v>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>登録ユーザー（累計）</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="9" t="n">
-        <v>9500</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>11200</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>13100</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>15200</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>17500</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>19500</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>21300</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>23300</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>25800</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>28500</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>31500</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>35000</v>
-      </c>
-      <c r="O37" s="16" t="n">
-        <v>35000</v>
-      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>有料会員（累計）</t>
+          <t>登録ユーザー（累計）</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>1140</v>
+        <v>9500</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1344</v>
+        <v>11200</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1572</v>
+        <v>13100</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>1824</v>
+        <v>15200</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>2100</v>
+        <v>17500</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>2340</v>
+        <v>19500</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2769</v>
+        <v>21300</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>3029</v>
+        <v>23300</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>3354</v>
+        <v>25800</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>3705</v>
+        <v>28500</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>4095</v>
+        <v>31500</v>
       </c>
       <c r="N38" s="7" t="n">
-        <v>4550</v>
+        <v>35000</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>4550</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  うち配信者プラン</t>
+          <t>有料会員（累計）</t>
         </is>
       </c>
       <c r="B39" s="19" t="n"/>
       <c r="C39" s="9" t="n">
-        <v>798</v>
+        <v>1140</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>941</v>
+        <v>1344</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>1101</v>
+        <v>1572</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>1277</v>
+        <v>1824</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>1470</v>
+        <v>2100</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>1638</v>
+        <v>2340</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1939</v>
+        <v>2769</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2121</v>
+        <v>3029</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2348</v>
+        <v>3354</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>2594</v>
+        <v>3705</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>2867</v>
+        <v>4095</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>3185</v>
+        <v>4550</v>
       </c>
       <c r="O39" s="16" t="n">
-        <v>3185</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  うちチームプラン</t>
+          <t xml:space="preserve">  うち配信者プラン</t>
         </is>
       </c>
       <c r="B40" s="18" t="n"/>
       <c r="C40" s="7" t="n">
+        <v>798</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>941</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1277</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>1470</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>1638</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>1939</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>2121</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>2348</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>2594</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>2867</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>3185</v>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  うちチームプラン</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="9" t="n">
         <v>342</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D41" s="9" t="n">
         <v>403</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E41" s="9" t="n">
         <v>471</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F41" s="9" t="n">
         <v>547</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G41" s="9" t="n">
         <v>630</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H41" s="9" t="n">
         <v>702</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I41" s="9" t="n">
         <v>830</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J41" s="9" t="n">
         <v>908</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K41" s="9" t="n">
         <v>1006</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="L41" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M41" s="9" t="n">
         <v>1228</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N41" s="9" t="n">
         <v>1365</v>
       </c>
-      <c r="O40" s="15" t="n">
+      <c r="O41" s="16" t="n">
         <v>1365</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>※ 本計画は見込み数値です。借入条件: 700万円 / 5年返済 / 年利2.0%想定</t>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>※ 本計画は見込み数値です。借入条件: 公庫350万 + 埼玉りそな350万 = 700万円協調融資 / 5年返済 / 年利2.0%想定 / 2026年5月末着金 → 6月1日正式ローンチ → 6月から返済開始</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A43:O43"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A36:O36"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A21:O21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -3811,7 +3905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3834,14 +3928,14 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LIVE SPOtCH  月次損益計算書（Year 3: 2028年7月〜2029年6月）</t>
+          <t>LIVE SPOtCH  月次損益計算書（Year 3: 2028年6月〜2029年5月）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIN-NAH株式会社 ／ 単位: 円</t>
+          <t>LIN-NAH株式会社 ／ 単位: 円 ／ v2改訂版（2026/05/11）</t>
         </is>
       </c>
     </row>
@@ -3855,62 +3949,62 @@
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>2028/6</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>2028/7</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2028/8</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>2028/9</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2028/10</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>2028/11</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>2028/12</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2029/1</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>2029/2</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>2029/3</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>2029/4</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>2029/5</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>2029/6</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -4200,982 +4294,1029 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>LiveKit Cloud（映像配信）</t>
+          <t>LiveKit Cloud Ship（映像配信）</t>
         </is>
       </c>
       <c r="B13" s="19" t="n"/>
       <c r="C13" s="9" t="n">
-        <v>80075</v>
+        <v>82575</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>87875</v>
+        <v>90375</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>96650</v>
+        <v>99150</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>106400</v>
+        <v>108900</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>116150</v>
+        <v>118650</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>124925</v>
+        <v>127425</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>134675</v>
+        <v>137175</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>145400</v>
+        <v>147900</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>157100</v>
+        <v>159600</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>169775</v>
+        <v>172275</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>183425</v>
+        <v>185925</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>200000</v>
+        <v>202500</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1602450</v>
+        <v>1632450</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Supabase（DB・認証）</t>
+          <t>TCP化中継server（B案・配信安定）</t>
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>270000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Vercel（ホスティング）</t>
+          <t>Supabase（DB・認証）</t>
         </is>
       </c>
       <c r="B15" s="19" t="n"/>
       <c r="C15" s="9" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>120000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Stripe手数料（3.6%）</t>
+          <t>Vercel（ホスティング）</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>66661</v>
+        <v>10000</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>73587</v>
+        <v>10000</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>81381</v>
+        <v>10000</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>90043</v>
+        <v>10000</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>98697</v>
+        <v>10000</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>106491</v>
+        <v>10000</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>115145</v>
+        <v>10000</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>124675</v>
+        <v>10000</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>135064</v>
+        <v>10000</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>146314</v>
+        <v>10000</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>158439</v>
+        <v>10000</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>173160</v>
+        <v>10000</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>1369657</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>その他インフラ</t>
+          <t>Stripe手数料（3.6%）</t>
         </is>
       </c>
       <c r="B17" s="19" t="n"/>
       <c r="C17" s="9" t="n">
+        <v>66661</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>73587</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>81381</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>90043</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>98697</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>106491</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>115145</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>124675</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>135064</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>146314</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>158439</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>173160</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>1369657</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>その他インフラ</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="N17" s="9" t="n">
+      <c r="N18" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O18" s="7" t="n">
         <v>24000</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>インフラ費 小計</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="21" t="n">
-        <v>173736</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>188462</v>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>205031</v>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>233443</v>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>251847</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>268416</v>
-      </c>
-      <c r="I18" s="21" t="n">
-        <v>286820</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>307075</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>329164</v>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>353089</v>
-      </c>
-      <c r="M18" s="21" t="n">
-        <v>378864</v>
-      </c>
-      <c r="N18" s="21" t="n">
-        <v>410160</v>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>3386107</v>
-      </c>
-    </row>
-    <row r="19" ht="8" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="21" t="n">
+        <v>177736</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>192462</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>209031</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>237443</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>255847</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>272416</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>290820</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>311075</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>333164</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>357089</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>382864</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>414160</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>3434107</v>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>販管費</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>開発費（保守・新機能）</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="O21" s="9" t="n">
-        <v>1800000</v>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>マーケティング費</t>
+          <t>開発費（保守・新機能）</t>
         </is>
       </c>
       <c r="B22" s="18" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>4800000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>人件費（CS・運営）</t>
+          <t>マーケティング費</t>
         </is>
       </c>
       <c r="B23" s="19" t="n"/>
       <c r="C23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>4200000</v>
+        <v>4800000</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>その他経費</t>
+          <t>人件費（CS・運営）</t>
         </is>
       </c>
       <c r="B24" s="18" t="n"/>
       <c r="C24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>その他経費</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N25" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O25" s="9" t="n">
         <v>600000</v>
       </c>
     </row>
-    <row r="25" ht="8" customHeight="1"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26" ht="8" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>経費 合計（返済前）</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="21" t="n">
-        <v>1123736</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>1138462</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>1155031</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>1183443</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>1201847</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>1218416</v>
-      </c>
-      <c r="I26" s="21" t="n">
-        <v>1236820</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <v>1257075</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>1279164</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <v>1303089</v>
-      </c>
-      <c r="M26" s="21" t="n">
-        <v>1328864</v>
-      </c>
-      <c r="N26" s="21" t="n">
-        <v>1360160</v>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>14786107</v>
-      </c>
-    </row>
-    <row r="27" ht="8" customHeight="1"/>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="21" t="n">
+        <v>1127736</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>1142462</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>1159031</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>1187443</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>1205847</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>1222416</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>1240820</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>1261075</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>1283164</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>1307089</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>1332864</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>1364160</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>14834107</v>
+      </c>
+    </row>
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>営業損益（返済前）</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="14" t="n">
-        <v>1266464</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>1548138</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>1852569</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>2169757</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>2496753</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>2801184</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>3128180</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>3478125</v>
-      </c>
-      <c r="K28" s="14" t="n">
-        <v>3850636</v>
-      </c>
-      <c r="L28" s="14" t="n">
-        <v>4245711</v>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>4663736</v>
-      </c>
-      <c r="N28" s="14" t="n">
-        <v>5149840</v>
-      </c>
-      <c r="O28" s="24" t="n">
-        <v>36651093</v>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="14" t="n">
+        <v>1262464</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>1544138</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1848569</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>2165757</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>2492753</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>2797184</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>3124180</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>3474125</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>3846636</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>4241711</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>4659736</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>5145840</v>
+      </c>
+      <c r="O29" s="24" t="n">
+        <v>36603093</v>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>借入返済</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>月額返済（5年/2.0%/¥122,694）</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="L31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="N31" s="9" t="n">
-        <v>122694</v>
-      </c>
-      <c r="O31" s="9" t="n">
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>122694</v>
+      </c>
+      <c r="O32" s="7" t="n">
         <v>1472328</v>
       </c>
     </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>返済後キャッシュフロー</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="14" t="n">
-        <v>1143770</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>1425444</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>1729875</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>2047063</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>2374059</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>2678490</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>3005486</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>3355431</v>
-      </c>
-      <c r="K33" s="14" t="n">
-        <v>3727942</v>
-      </c>
-      <c r="L33" s="14" t="n">
-        <v>4123017</v>
-      </c>
-      <c r="M33" s="14" t="n">
-        <v>4541042</v>
-      </c>
-      <c r="N33" s="14" t="n">
-        <v>5027146</v>
-      </c>
-      <c r="O33" s="24" t="n">
-        <v>35178765</v>
-      </c>
-    </row>
+    <row r="33" ht="8" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>累計CF（返済後）</t>
+          <t>返済後キャッシュフロー</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
       <c r="C34" s="14" t="n">
-        <v>1265979</v>
+        <v>1139770</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>2691423</v>
+        <v>1421444</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>4421298</v>
+        <v>1725875</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>6468361</v>
+        <v>2043063</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>8842420</v>
+        <v>2370059</v>
       </c>
       <c r="H34" s="14" t="n">
-        <v>11520910</v>
+        <v>2674490</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>14526396</v>
+        <v>3001486</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>17881827</v>
+        <v>3351431</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>21609769</v>
+        <v>3723942</v>
       </c>
       <c r="L34" s="14" t="n">
-        <v>25732786</v>
+        <v>4119017</v>
       </c>
       <c r="M34" s="14" t="n">
-        <v>30273828</v>
+        <v>4537042</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>35300974</v>
-      </c>
-      <c r="O34" s="14" t="n">
-        <v>35300974</v>
-      </c>
-    </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+        <v>5023146</v>
+      </c>
+      <c r="O34" s="24" t="n">
+        <v>35130765</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>累計CF（返済後）</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="14" t="n">
+        <v>1165979</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>2587423</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>4313298</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>6356361</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>8726420</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>11400910</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>14402396</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>17753827</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>21477769</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>25596786</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>30133828</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>35156974</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>35156974</v>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>登録ユーザー（累計）</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="9" t="n">
-        <v>38500</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>42500</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>47000</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>52000</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>57000</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>61500</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>66500</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>72000</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>78000</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>84500</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>91500</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="O37" s="16" t="n">
-        <v>100000</v>
-      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>有料会員（累計）</t>
+          <t>登録ユーザー（累計）</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>5005</v>
+        <v>38500</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>5525</v>
+        <v>42500</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>6110</v>
+        <v>47000</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>6760</v>
+        <v>52000</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>7410</v>
+        <v>57000</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>7995</v>
+        <v>61500</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>8645</v>
+        <v>66500</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>9360</v>
+        <v>72000</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>10140</v>
+        <v>78000</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>10985</v>
+        <v>84500</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>11895</v>
+        <v>91500</v>
       </c>
       <c r="N38" s="7" t="n">
-        <v>13000</v>
+        <v>100000</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>13000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  うち配信者プラン</t>
+          <t>有料会員（累計）</t>
         </is>
       </c>
       <c r="B39" s="19" t="n"/>
       <c r="C39" s="9" t="n">
-        <v>3254</v>
+        <v>5005</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>3592</v>
+        <v>5525</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>3972</v>
+        <v>6110</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>4394</v>
+        <v>6760</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4817</v>
+        <v>7410</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5197</v>
+        <v>7995</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>5620</v>
+        <v>8645</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>6084</v>
+        <v>9360</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>6591</v>
+        <v>10140</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>7141</v>
+        <v>10985</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>7732</v>
+        <v>11895</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>8450</v>
+        <v>13000</v>
       </c>
       <c r="O39" s="16" t="n">
-        <v>8450</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  うちチームプラン</t>
+          <t xml:space="preserve">  うち配信者プラン</t>
         </is>
       </c>
       <c r="B40" s="18" t="n"/>
       <c r="C40" s="7" t="n">
+        <v>3254</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>3592</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>3972</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>4394</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>4817</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>5197</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>5620</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>6084</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>6591</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>7141</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>7732</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>8450</v>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>8450</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  うちチームプラン</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="9" t="n">
         <v>1751</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D41" s="9" t="n">
         <v>1933</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E41" s="9" t="n">
         <v>2138</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F41" s="9" t="n">
         <v>2366</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G41" s="9" t="n">
         <v>2593</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H41" s="9" t="n">
         <v>2798</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I41" s="9" t="n">
         <v>3025</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J41" s="9" t="n">
         <v>3276</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K41" s="9" t="n">
         <v>3549</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="L41" s="9" t="n">
         <v>3844</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M41" s="9" t="n">
         <v>4163</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N41" s="9" t="n">
         <v>4550</v>
       </c>
-      <c r="O40" s="15" t="n">
+      <c r="O41" s="16" t="n">
         <v>4550</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>※ 本計画は見込み数値です。借入条件: 700万円 / 5年返済 / 年利2.0%想定</t>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>※ 本計画は見込み数値です。借入条件: 公庫350万 + 埼玉りそな350万 = 700万円協調融資 / 5年返済 / 年利2.0%想定 / 2026年5月末着金 → 6月1日正式ローンチ → 6月から返済開始</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A43:O43"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A36:O36"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A21:O21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -5189,17 +5330,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>収支計画の前提条件</t>
+          <t>収支計画の前提条件 (v2 改訂版)</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5351,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>【料金設定】</t>
+          <t>【ローンチタイムライン (v2)】</t>
         </is>
       </c>
       <c r="B4" s="27" t="inlineStr"/>
@@ -5218,132 +5359,132 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>配信者プラン月額</t>
+          <t>提案書 v1.0 提出予定</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>¥300</t>
+          <t>2026/5/16 (早期提出版)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>チームプラン月額</t>
+          <t>借入着金予定</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>¥500</t>
+          <t>2026/5/末 (公庫350万 + 埼玉りそな350万)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>アーカイブ課金（1ヶ月経過後）</t>
+          <t>正式ローンチ予定</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>¥100/回</t>
+          <t>2026/6/1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr"/>
-      <c r="B8" s="25" t="inlineStr"/>
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Phase 0 完璧化期</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>2026/5/10 - 5/31 (3週)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>【転換率】</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr"/>
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1 ローンチ期</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>2026/6/1 - 7/31 (8週)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>有料転換率（Year 1前半）</t>
+          <t>KPI ゲート1: 有料5名</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>8〜10%</t>
+          <t>2026/6/7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>有料転換率（Year 1後半）</t>
+          <t>KPI ゲート2: 有料20名</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>10〜12.5%</t>
+          <t>2026/8/6</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>有料転換率（Year 2）</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>12〜13%</t>
-        </is>
-      </c>
+      <c r="A12" s="25" t="inlineStr"/>
+      <c r="B12" s="25" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>有料転換率（Year 3）</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>13%</t>
-        </is>
-      </c>
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>【料金設定 (v2: 2026/4/30 確定)】</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>チームプラン比率（Year 1）</t>
+          <t>配信者プラン月額</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>¥300 (ライブ専用、アーカイブなし)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>チームプラン比率（Year 2）</t>
+          <t>チームプラン月額</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>¥500 (+YouTube Live同時配信+アーカイブ+チーム管理)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>チームプラン比率（Year 3）</t>
+          <t>アーカイブ課金 (1ヶ月経過後)</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>¥100/視聴 (チームプラン配信のみ)</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5495,7 @@
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>【ユーザー目標（PPTと統一）】</t>
+          <t>【転換率】</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr"/>
@@ -5362,274 +5503,430 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>Year 1末 登録ユーザー</t>
+          <t>有料転換率（Year 1前半）</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>8,000人</t>
+          <t>8〜10%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>Year 1末 有料会員</t>
+          <t>有料転換率（Year 1後半）</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>約1,000人</t>
+          <t>10〜12.5%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>Year 2末 登録ユーザー</t>
+          <t>有料転換率（Year 2）</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>35,000人</t>
+          <t>12〜13%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>Year 2末 有料会員</t>
+          <t>有料転換率（Year 3）</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>約4,500人</t>
+          <t>13%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>Year 3末 登録ユーザー</t>
+          <t>チームプラン比率（Year 1）</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>100,000人</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>Year 3末 有料会員</t>
+          <t>チームプラン比率（Year 2）</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>約13,000人</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr"/>
-      <c r="B25" s="25" t="inlineStr"/>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>チームプラン比率（Year 3）</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>【インフラ】</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr"/>
+      <c r="A26" s="25" t="inlineStr"/>
+      <c r="B26" s="25" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>LiveKit Cloud</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>¥5,000/月 + 有料会員×¥15</t>
-        </is>
-      </c>
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>【ユーザー目標（PPTと統一）】</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Year 1末 登録ユーザー</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>¥3,000〜25,000（段階制）</t>
+          <t>8,000人</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Year 1末 有料会員</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>¥2,500〜10,000（段階制）</t>
+          <t>約1,000人</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>Stripe手数料</t>
+          <t>Year 2末 登録ユーザー</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>売上の3.6%</t>
+          <t>35,000人</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr"/>
-      <c r="B31" s="25" t="inlineStr"/>
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Year 2末 有料会員</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>約4,500人</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>【広告収入】</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="inlineStr"/>
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Year 3末 登録ユーザー</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>100,000人</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>広告開始時期</t>
+          <t>Year 3末 有料会員</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Year 2後半（19ヶ月目〜）</t>
+          <t>約13,000人</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>初期広告単価</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>¥50,000/月〜</t>
-        </is>
-      </c>
+      <c r="A34" s="25" t="inlineStr"/>
+      <c r="B34" s="25" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="inlineStr"/>
-      <c r="B35" s="25" t="inlineStr"/>
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>【インフラ費 (v2: 5/10 LiveKit Ship 昇格反映)】</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>【借入条件】</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr"/>
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>LiveKit Cloud Ship</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>¥7,500/月 (Egress 600分含み) + 有料会員×¥15</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>借入金額</t>
+          <t>TCP化中継 server (B 案)</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>¥7,000,000</t>
+          <t>¥1,500/月 (Cloudflare Workers / Fly.io 等)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>返済期間</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>5年（60回）</t>
+          <t>¥3,000〜25,000 (段階制)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>想定利率</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>年2.0%</t>
+          <t>¥2,500〜10,000 (段階制)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>月額返済額</t>
+          <t>Stripe手数料</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>¥122,694</t>
+          <t>売上の3.6%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>年間返済額</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>¥1,472,328</t>
-        </is>
-      </c>
+      <c r="A41" s="25" t="inlineStr"/>
+      <c r="B41" s="25" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr"/>
-      <c r="B42" s="25" t="inlineStr"/>
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>【広告収入】</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
-        <is>
-          <t>【その他】</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="inlineStr"/>
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>広告開始時期</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Year 2後半（19ヶ月目〜）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>ローンチ時期</t>
+          <t>初期広告単価</t>
         </is>
       </c>
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>2026年7月</t>
+          <t>¥50,000/月〜</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="25" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr"/>
+      <c r="B45" s="25" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>【借入条件 (v2: 協調融資)】</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>総借入金額</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>¥7,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>内訳: 日本政策金融公庫</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>¥3,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>内訳: 埼玉りそな銀行</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>¥3,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>返済期間</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>5年（60回）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>想定利率</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>年2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>月額返済額</t>
+        </is>
+      </c>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>¥122,694</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>年間返済額</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>¥1,472,328</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>着金予定</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>2026年5月末</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>返済開始</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>2026年6月 (ローンチ同月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr"/>
+      <c r="B56" s="25" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>【その他】</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>正式ローンチ時期</t>
+        </is>
+      </c>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>2026年6月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>黒字化目標</t>
         </is>
       </c>
-      <c r="B45" s="25" t="inlineStr">
+      <c r="B59" s="25" t="inlineStr">
         <is>
           <t>Year 2中盤（18ヶ月目前後）</t>
         </is>
@@ -5663,7 +5960,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>借入金返済スケジュール（700万円 / 5年 / 年利2.0%）</t>
+          <t>借入金返済スケジュール（700万円 / 5年 / 年利2.0% / 2026/6 開始）</t>
         </is>
       </c>
     </row>
